--- a/INFORME_CLINICO_FINAL.xlsx
+++ b/INFORME_CLINICO_FINAL.xlsx
@@ -473,10 +473,10 @@
         <v>359.99</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="F2" t="n">
         <v>53.39</v>
@@ -505,10 +505,10 @@
         <v>359.94</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>107.35</v>
       </c>
       <c r="F3" t="n">
         <v>48.32</v>
@@ -537,10 +537,10 @@
         <v>359.97</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>106.67</v>
       </c>
       <c r="F4" t="n">
         <v>43.66</v>
@@ -569,10 +569,10 @@
         <v>359.97</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>81.67</v>
       </c>
       <c r="F5" t="n">
         <v>59.14</v>
@@ -601,10 +601,10 @@
         <v>359.99</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>593</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>98.84</v>
       </c>
       <c r="F6" t="n">
         <v>59.77</v>
@@ -633,10 +633,10 @@
         <v>359.99</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
         <v>60.75</v>
@@ -665,10 +665,10 @@
         <v>359.97</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>105.67</v>
       </c>
       <c r="F8" t="n">
         <v>44.07</v>
@@ -697,10 +697,10 @@
         <v>359.98</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>104.34</v>
       </c>
       <c r="F9" t="n">
         <v>29.02</v>
@@ -729,10 +729,10 @@
         <v>359.98</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>87.17</v>
       </c>
       <c r="F10" t="n">
         <v>53.08</v>
@@ -761,10 +761,10 @@
         <v>359.98</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>114.34</v>
       </c>
       <c r="F11" t="n">
         <v>54.88</v>
@@ -793,10 +793,10 @@
         <v>359.97</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>76.34</v>
       </c>
       <c r="F12" t="n">
         <v>54.8</v>
@@ -825,10 +825,10 @@
         <v>359.97</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>114.68</v>
       </c>
       <c r="F13" t="n">
         <v>52.4</v>
@@ -857,10 +857,10 @@
         <v>359.98</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="F14" t="n">
         <v>47.83</v>
@@ -889,10 +889,10 @@
         <v>361</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>71.14</v>
       </c>
       <c r="F15" t="n">
         <v>53.88</v>
@@ -921,10 +921,10 @@
         <v>359.98</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>105.67</v>
       </c>
       <c r="F16" t="n">
         <v>46.22</v>
@@ -953,10 +953,10 @@
         <v>359.98</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>583</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>97.17</v>
       </c>
       <c r="F17" t="n">
         <v>54.52</v>
@@ -985,10 +985,10 @@
         <v>359.99</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F18" t="n">
         <v>39.68</v>
@@ -1017,10 +1017,10 @@
         <v>359.96</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>97.34</v>
       </c>
       <c r="F19" t="n">
         <v>33.61</v>
@@ -1049,10 +1049,10 @@
         <v>168.6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>100.71</v>
       </c>
       <c r="F20" t="n">
         <v>39.17</v>
@@ -1081,10 +1081,10 @@
         <v>359.98</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>107.01</v>
       </c>
       <c r="F21" t="n">
         <v>62.48</v>
@@ -1113,10 +1113,10 @@
         <v>359.99</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>91.34</v>
       </c>
       <c r="F22" t="n">
         <v>36.4</v>

--- a/INFORME_CLINICO_FINAL.xlsx
+++ b/INFORME_CLINICO_FINAL.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID_Paciente</t>
+          <t>CodeID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -454,7 +454,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Error_Reason</t>
         </is>
       </c>
     </row>
@@ -489,6 +494,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,6 +527,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,6 +560,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -585,6 +593,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +626,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -649,6 +659,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -681,6 +692,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,7 +722,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>WARN_BIOMECH_OUT_OF_BOUNDS (Fase apoyo anómala)</t>
         </is>
       </c>
     </row>
@@ -745,6 +762,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -777,6 +795,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -809,6 +828,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -841,6 +861,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -873,6 +894,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -905,6 +927,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -937,6 +960,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -969,6 +993,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1001,6 +1026,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1033,6 +1059,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1065,6 +1092,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1097,6 +1125,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1129,6 +1158,7 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
